--- a/request_forms/040_special_request_form--request_forms.xlsx
+++ b/request_forms/040_special_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Special Request Form Description</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>special_request_form</t>
+          <t>special_request_form_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Special Request Form</t>
+          <t>Special Request Form 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>special_request_form</t>
+          <t>special_request_form_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Special Request Form</t>
+          <t>Special Request Form 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -779,7 +779,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -872,7 +872,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -906,7 +906,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>special_request_form_choices</t>
+          <t>special_request_form_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -923,7 +923,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>special_request_form_choices</t>
+          <t>special_request_form_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -974,7 +974,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>special_request_form_choices</t>
+          <t>special_request_form_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>special_request_form_choices</t>
+          <t>special_request_form_3_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
